--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4579,6 +4579,96 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>入营名单</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>黑客松夏令营</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>已进入夏令营选拔 (字段)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>在 dtlms_plan_offer 增加布尔字段 is_in_camp_selection (中文显示已进入夏令营选拔), 含 SQL 迁移脚本</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>列表展示已入夏令营选拔</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>在 /recruitment/camp-offers 列表增加 "已入夏令营选拔" 列, 是/否 展示</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>编辑对话框开关控件</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>编辑/新增入营名单对话框中增加 "已进入夏令营选拔" 开关, 是/否 切换; 仅作标记, 不改变入营业务</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>导入夏令营选拔的学生</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>新增 "导入夏令营选拔的学生" 按钮 + 弹窗; Excel 表头 "报名号 / 夏令营选拔" (是/否), 通过报名号匹配入营名单, 仅更新 is_in_camp_selection; 未匹配行跳过并在下方报告 (不报错)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="52">
     <mergeCell ref="B136:B170"/>
@@ -4591,9 +4681,9 @@
     <mergeCell ref="C120:C122"/>
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C23:C27"/>
     <mergeCell ref="C136:C143"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="C53:C55"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4664,6 +4664,116 @@
         </is>
       </c>
       <c r="F178" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>入营名单</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>黑客松夏令营</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>夏令营选拔环节查询</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>在 dtlms_plan_offer 按 candidate_no + plan_id 查询 is_in_camp_selection (postgres_state_store_query_recruitment.find_camp_offer_is_in_camp_selection), 用于门户进度判断</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>去掉初筛环节 (门户首页 UI)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>从 /portal/home 的「申请环节状态」中移除「初筛」卡片; stages 由 7 贴减为 6 (在线申请/资料审核/背景评估/夏令营选拔/结果公布/预取录)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>在初筛中 → 进入夏令营选拔</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>学生 application_status 处于 {待导师初筛, 待导师初筛-第一志愿, 待导师初筛-第二志愿, 待初筛确认} 且 is_in_camp_selection=true 时, 背景评估 completed, 夏令营选拔 current</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>在初筛中 → 停留在背景评估</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>学生同上但 is_in_camp_selection=false 或未查到, 背景评估 current (停留), 夏令营选拔 不浮现</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>初筛未通过终止·跳转</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>原 _portal_terminated_stage_start_key 在初筛未通过时返回 'initial_screening', 现已不再有该 stage, 改为 'background_review' (UI 上不再有初筛卡)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -4682,8 +4792,8 @@
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
     <mergeCell ref="C23:C27"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C136:C143"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="C53:C55"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4779,6 +4779,36 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>入营名单</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>黑客松夏令营</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>夏令营选拔筛选与统计</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>在 /recruitment/camp-offers 筛选区追加"夏令营选拔 [全部/是/否]" (按 dtlms_plan_offer.is_in_camp_selection 过滤); KPI 区"未签署"右侧追加"已入选拔"统计卡 (is_in_camp_selection=TRUE 计数), 整体 5 列 × 2 行 栅格布局 (最后一格留空); 后端 API /camp-offers 与 /camp-offers/stats 加 is_in_camp_selection Query 参数, store 层同步加入 where 子句与聚合统计.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="52">
     <mergeCell ref="B136:B170"/>
@@ -4791,8 +4821,8 @@
     <mergeCell ref="C120:C122"/>
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C23:C27"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C136:C143"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="14055" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="功能模块清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能模块清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5703,6 +5703,136 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>需以管理员 PowerShell 跑 schtasks /Create /TN pydtlms-weekly-review /XML ... 注册调度任务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>186</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>录取通知书卡片</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>portal 端 /portal/home/offer</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>新增 /portal/home/offer 路由 (PortalHomeOfferView); 独立端点 GET /api/v1/portal/offer 返回 admission_offered_school / accepted_notification_sent_at; 字典 录取通知学生未签署超时小时 (默认 24) 控制超时阈值; 卡片展示录取学校 / 落款日期 / 剩余确认时间 / 接受&amp;拒绝 (本轮 disable 占位).</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>187</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>录取通知书卡片</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>字典规范名重命名</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>将 /portal/home/offer 卡片超时阈值字典的 dict_type 从 中文名「录取通知学生未签署超时小时」改为英文规范名 student_signed_offer_timeout_hours, dict_name 改为「学生签署录取通知超时小时」; 数据库 dtlms_dict_types.id=9574 与 dtlms_dict_data.id=51514 实际行已 UPDATE 同步; 前端 listDictData 调用的 dict_type 同步更新; 字典数据 value=24, label=24 小时 保持不变.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>AGENTS.md 备份规则 + UTF-8 写入 + DB 实际执行均已完成; xlsx 仅追加行, 未改列/合并/样式.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>188</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>录取通知书卡片</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SQL 脚本 update20260707.sql</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>backend/sql/update20260707.sql 中 字典 INSERT 段 (DO \$) dict_type/dict_name 已改写为规范名, header 注释按 dict_type / dict_name 各自一行; 脚本可重复执行 (IF NOT EXISTS 仍按新 dict_type 判定); 备份: update20260707_20260707201800.sql.bak.</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>本轮仅改 dict_type/dict_name; ALTER TABLE 段保持不变.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>189</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>录取通知书卡片</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>前端 listDictData 调用同步</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>PortalHomeOfferView.vue 中 listDictData({ dict_type: ... }) 参数同步改为 student_signed_offer_timeout_hours; 备份: PortalHomeOfferView_20260707202000.vue.bak.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
     </row>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5836,6 +5836,176 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>190</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>入营名单</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>录取决议权限收紧</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>can_change_accepted 简化</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>后端 postgres_state_store_query_recruitment.py 的 can_change_accepted SQL 从 5 条件 (is_unrestricted + is_center_leader + 2 套"我是学生具体导师+分数≥80") 简化为 2 条件 (is_unrestricted + is_center_leader). can_change_params 列表从 5 元素 → 2 元素 (2 处: list_camp_offers_page / get_camp_offer_detail). 业务影响: 普通 advisor 完全无 can_change_accepted 权限 (不再"我是学生具体导师+分数≥80"能改); 中心负责人对自己可见列表里所有学生均可改 (不再要求是学生具体导师). 前端 el-table 按钮可见性只依赖 can_change_accepted + rowHasHackathonEvaluation, 无需改.</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>后端 store 层 SQL + Python 注入逻辑 同步简化; 备份: postgres_state_store_query_recruitment_20260709150000.py.bak; 已用 psycopg 直连测试 4 种角色场景, 输出与新规则一致.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>191</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>入营名单</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>录取决议权限收紧</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SQL 注释同步</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>backend/sql/update20260709.sql 链 B 步骤 3 加"权限收紧"段: 明确"仅 is_center_leader=True (研究中心负责人) 或 is_unrestricted=True (书院/平台) 可改; 普通 advisor 完全不允许; 中心负责人对自己可见列表里所有学生均可改 (不再要求是学生具体导师)". 删除原"普通 advisor 仅在 first/second_choice 分数 ≥ 80 时可改 accepted"的过时规则. 备份: update20260709_20260709150000.sql.bak.</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>本轮仅改注释, 未改 DDL; 数据库实际未变, 无需执行.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>192</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>接受/拒绝 前后端</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>portal 端 accept/reject API</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>后端: 新增 POST /api/v1/portal/offer/accept + /reject 端点 (api/v1/portal.py). management_service_portal.py 加 accept_portal_offer / reject_portal_offer / _change_portal_offer / _resolve_offer_timeout_hours 4 个方法. postgres_state_store_query_recruitment.py 加 update_camp_offer_accepted_by_student SQL 方法 (守门条件: WHERE accepted = expected_current_accepted 防并发). schemas/portal.py PortalOfferRecord 加 accepted / student_submitted_offer_at 字段. 后端校验: 1) accepted 必须为 accepted_sent; 2) accepted_notification_sent_at + dict.student_signed_offer_timeout_hours 小时 &gt; now() (字典 fallback 24). 失败: 400 / 403 + 错误 message. 写库: dtlms_plan_offer SET accepted = accepted_confirmed/accepted_rejected + student_submitted_offer_at = now() + updated_at = now() (表无 trigger, 显式写). 前端: portal.ts 加 acceptPortalOffer / rejectPortalOffer + PortalOfferRecord 类型扩展. PortalHomeOfferView.vue 加 onAcceptOffer / onDeclineOffer (ElMessageBox 二次确认 + loading + 错误提示). 按钮: 去掉 disabled, 联动 canChangeOffer (accepted=accepted_sent &amp;&amp; !expired). 已签/已拒时按钮置灰 + 显示"您已于 YYYY-MM-DD HH:MM 接受/拒绝".</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>后端 8 个文件 + 前端 5 个文件; 备份 *_20260709180000.*.bak; py_compile + vue-tsc 双绿.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>193</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>接受/拒绝 前后端</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>portal 登录后自动跳转</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>PortalHomeView.vue (/portal/home) onMounted 加 tryRedirectToOfferIfNeeded(): 调 GET /portal/offer 拿 accepted, 若 accepted IN (accepted_sent, accepted_confirmed, accepted_rejected) → router.replace(/portal/home/offer). 不阻塞主页加载 (异步). 失败时静默, 留在 /portal/home. router/index.ts meta.title 从 "Offer 签署 (待改造)" 改为 "录取通知书签署".</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>194</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>录取通知书邮件发送</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>管理端 send-offer-notification API</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>后端: 新增 POST /api/v1/recruitment/camp-offers/send-offer-notification 端点 (api/v1/recruitment.py). management_service_recruitment.py 加 send_offer_notifications + _resolve_offer_timeout_hours. email_service.py 加 send_admission_offer_letter 方法 (与 portal 卡片同源文案). schemas/recruitment.py 加 SendAdmissionOfferNotificationRequest / Response / Item 3 个 schema. 业务规则: accepted IN (accepted_pending_send, accepted_confirmed, accepted_rejected) 允许重发; declined/pending 不允许. 写库: accepted=accepted_sent + accepted_notification_sent_at=now() + 清空 student_submitted_offer_at. 发邮件: 实际收件人统一替换为 lk139@126.com (测试期). 返回 {sent, failed, skipped}. 前端: recruitment.ts 加 sendAdmissionOfferNotifications + 类型; CampOfferListView.vue 弹窗"确认发送"按钮去掉 disabled, 加 loading, 调后端 + 刷新列表 + 显示结果. 注意: 现有 /recruitment/camp-offers/notify 端点 (sent_mail_at 那条线) 与本端点功能区分, 不要混淆.</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>AGENTS.md 5.2 状态机不变量 + 5.3 邮件测试邮箱已记录; 5.4 跳转条件已记录; 5.5 备份失误备忘已记录.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="B136:B170"/>
@@ -5849,8 +6019,8 @@
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
     <mergeCell ref="C23:C27"/>
+    <mergeCell ref="C136:C143"/>
     <mergeCell ref="B28:B36"/>
-    <mergeCell ref="C136:C143"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="C53:C55"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6006,6 +6006,136 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>195</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>录取通知书邮件发送</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>HTML 模板 + SMTP_SEND_MODE + 真实 student_name</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>邮件模板升级: email_service.send_admission_offer_letter 改用 multipart/alternative (text/plain + text/html) 双格式. HTML 与 portal /portal/home/offer 卡片同源 (Shanghai AI Lab 品牌徽 + ADMISSION LETTER + 录取学校 + 落款日期 + 立即确认按钮). student_name 真实取值: send_offer_notifications 在 SQL 加 LEFT JOIN dtlms_portal_students ps ON ps.id=offer.portal_student_id AND ps.account_status=启用, 拿 ps.full_name + ps.email. student_name 兜底: 拿不到 full_name 时用 candidate_no. SMTP_SEND_MODE 配置: backend/app/core/config.py 加 smtp_send_mode 字段 (默认 real, env SMTP_SEND_MODE=mock/real). smtp_send_mode_normalized property (大小写不敏感). email_service 按 mode 决定收件人: mock -&gt; TEST_OVERRIDE_RECIPIENT (lk139@126.com); real -&gt; student_email (空时 fallback lk139@126.com). .env 不写 SMTP_SEND_MODE = real (默认). 新增 _send_multipart 私有方法 (复用 _format_from_address + _send_via_smtp + _record_delivery).</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>py_compile 通过; 关联查询实测能拿 full_name+email; 备份 *_20260709200000.*.bak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>196</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>录取通知书邮件发送</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>修复 _connect AttributeError</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>后端 bug 修复: 2026-07-10 /recruitment/camp-offers 选中发送录取通知邮件报错 RuntimeManagementStore object has no attribute _connect. 根因: send_offer_notifications 在 management service 层 (RuntimeManagementStore) 直接调 self._connect(), 但 _connect 是 postgres store 层 (postgres_state_store_query_recruitment.py) 的方法, service 层没有这个属性. 修复: 把 2 段 SQL 提到 store 层作为新方法 find_camp_offers_for_notification (查 offer + portal_student 关联) + mark_camp_offer_as_notification_sent (写库 accepted_sent + 时间 + 清空 student_submitted_offer_at + updated_at), service 层改走 self._postgres_store.xxx() 调用. 整个文件 self._connect 调用清零, 全走 self._postgres_store. 备份: *_20260710103000.*.bak.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>后端 3 个文件 (store/service/api); 验证 0 处 self._connect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>197</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>录取通知书邮件发送</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>发送进度条（单条循环）</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>改进 /recruitment/camp-offers 弹窗【发送录取通知】按钮的体验：不再一次性 POST /camp-offers/send-offer-notification 等后端整体返回，而是改为按 candidate_no 逐个 POST /camp-offers/send-offer-notification/one (后端 store.send_one_offer_notification)，前端用 el-progress 实时显示 【已处理 N / 总数】+ 当前 candidate_no + 实际模式 (mock/real) + 实际收件人。后端 schemas/recruitment.py 新增 SendOneAdmissionOfferNotificationRequest/Response，返回 {ok, reason, actual_recipient, actual_smtp_send_mode}。业务校验/状态机/写库字段 (accepted=accepted_sent, accepted_notification_sent_at=now(),清空 student_submitted_offer_at) 与批处理一致；mock 模式下实际收件人强制 lk139@126.com，真实模式下用 student_email (空时 fallback lk139@126.com)。验证：py_compile 后端 OK + vue-tsc 前端 OK。备份：*_20260710110000.*.bak。</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>198</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>录取通知书 / 已签署结果卡片</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>接受/拒绝结果视图</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>改进 /portal/home/offer 在已签署状态下的视图: 之前只在录取通知书卡片底部显示一行 【您已于 ... 接受/拒绝 录取】 小字, 客户反馈与设计稿不一致. 现在改为: 当 accepted IN (accepted_confirmed, accepted_rejected) 时, 整张录取通知书卡片替换为简洁结果视图: 圆形 ✓/× 图标 + 主标题 【恭喜！录取确认成功】或【你已拒绝本次录取】+ 三段说明文案 (与客户图 1/图 2 一致) + 底部您已于 ... 接受/拒绝 录取 时间戳. 外层 &lt;section class=portal-offer-card&gt; 容器保留, 内部用 &lt;template v-if=isOfferSigned&gt; 二选一, 不影响未签署状态的原有 ADMISSION LETTER 视图. CSS: 新增 .portal-offer-card__result / __result-icon / __result-title / __result-line / __result-line--accent / __result-time, 接受态绿色 (#67c23a), 拒绝态红色 (#f56c6c). 验证: vue-tsc --noEmit OK. 备份 PortalHomeOfferView_20260710112317.vue.bak.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="B136:B170"/>
@@ -6019,8 +6149,8 @@
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
     <mergeCell ref="C23:C27"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C136:C143"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="C53:C55"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6136,6 +6136,36 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>199</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>接受/拒绝按钮</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>互斥 disable (单次只允许 1 个 loading)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>修复 /portal/home/offer 接受/拒绝按钮可同时点击的 bug: 之前 onAcceptOffer 进入 loading 后, onDeclineOffer 仍 enabled, 导致同一时间可点两个按钮并发发起请求. 现两个按钮的 :disabled 增加 offerActionLoading.accept || offerActionLoading.reject 判断, 任一 loading 期间两个按钮均 disable; :loading 也同步合并显示 (接受按钮也会在拒绝请求中显示 loading). 验证: vue-tsc --noEmit OK. 备份 PortalHomeOfferView_20260710153216.vue.bak.</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="B136:B170"/>
@@ -6148,8 +6178,8 @@
     <mergeCell ref="C120:C122"/>
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C23:C27"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C136:C143"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>

--- a/documents/博士生生命周期管理功能模块说明.xlsx
+++ b/documents/博士生生命周期管理功能模块说明.xlsx
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6166,6 +6166,36 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>200</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Offer 签署</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>接受/拒绝按钮</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>二次确认弹出前就置 loading (修复上一轮修复无效)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>上一轮(行 199)虽然在两个按钮的 :disabled 里加了 offerActionLoading.accept || offerActionLoading.reject, 但 offerActionLoading.value.accept=true 是在 await ElMessageBox.confirm 之后才赋值, 所以点接受 -&gt; 弹二次确认框期间 offerActionLoading.accept 还是 false, 拒绝按钮此时仍然 enabled, 用户可在弹框期间点拒绝.本轮把 offerActionLoading.value.accept/reject = true 提到 await confirm 之前; 用户取消弹框时再复位. 这样点接受瞬间拒绝按钮就置灰, 点拒绝瞬间接受按钮就置灰.验证: vue-tsc --noEmit OK. 备份 PortalHomeOfferView_20260710161730.vue.bak.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="B136:B170"/>
@@ -6178,9 +6208,9 @@
     <mergeCell ref="C120:C122"/>
     <mergeCell ref="C162:C165"/>
     <mergeCell ref="C129:C135"/>
-    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C23:C27"/>
     <mergeCell ref="C136:C143"/>
+    <mergeCell ref="B28:B36"/>
     <mergeCell ref="C144:C148"/>
     <mergeCell ref="C45:C52"/>
     <mergeCell ref="C53:C55"/>
